--- a/data/trans_bre/P16A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,46</t>
+          <t>1,04; 8,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,91</t>
+          <t>0,15; 7,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 9,56</t>
+          <t>2,99; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,57</t>
+          <t>3,62; 9,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,44; 781,61</t>
+          <t>10,09; 730,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 771,07</t>
+          <t>-14,34; 636,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,61; 2648,25</t>
+          <t>71,2; 2978,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>107,02; 1231,82</t>
+          <t>121,23; 1558,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,57</t>
+          <t>0,17; 4,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,67</t>
+          <t>1,06; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,73</t>
+          <t>-0,5; 2,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,98</t>
+          <t>0,07; 2,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 551,95</t>
+          <t>-6,92; 590,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,96; 993,0</t>
+          <t>19,72; 901,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 512,77</t>
+          <t>-37,47; 553,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 543,2</t>
+          <t>-12,58; 642,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,08</t>
+          <t>1,44; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,51</t>
+          <t>1,75; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,47</t>
+          <t>1,01; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,54</t>
+          <t>0,37; 6,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 2016,57</t>
+          <t>13,12; 1874,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,14; 1353,86</t>
+          <t>44,87; 1606,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,9; —</t>
+          <t>15,77; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 240,81</t>
+          <t>0,52; 220,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,56</t>
+          <t>0,64; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,31</t>
+          <t>4,34; 10,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,2</t>
+          <t>3,45; 9,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,38</t>
+          <t>-1,54; 2,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 348,69</t>
+          <t>8,41; 349,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>154,35; 1771,11</t>
+          <t>121,54; 1706,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>116,65; 1191,24</t>
+          <t>109,5; 1382,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 645,64</t>
+          <t>-65,59; 584,35</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,98</t>
+          <t>2,05; 8,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,95</t>
+          <t>3,52; 12,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,87</t>
+          <t>0,7; 5,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,18</t>
+          <t>2,5; 9,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,12; 1763,51</t>
+          <t>60,86; 1872,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,8; 504,63</t>
+          <t>44,0; 588,95</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,73</t>
+          <t>1,84; 8,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,6</t>
+          <t>1,75; 7,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,34</t>
+          <t>0,44; 5,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,72</t>
+          <t>1,42; 6,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,02; 991,44</t>
+          <t>35,1; 1131,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,51; —</t>
+          <t>36,61; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,48; —</t>
+          <t>-15,98; 1747,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,73; 375,26</t>
+          <t>28,35; 353,99</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,93</t>
+          <t>0,99; 6,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,35</t>
+          <t>3,19; 7,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,15</t>
+          <t>-0,75; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,58</t>
+          <t>-2,13; 5,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,73; 279,49</t>
+          <t>20,28; 301,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>113,24; 1015,51</t>
+          <t>106,66; 1015,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 211,79</t>
+          <t>-22,97; 197,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 159,43</t>
+          <t>-38,27; 154,07</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,66</t>
+          <t>-0,73; 2,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,36</t>
+          <t>2,3; 5,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,22</t>
+          <t>1,31; 4,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,75</t>
+          <t>0,94; 2,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 168,62</t>
+          <t>-24,13; 163,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>138,82; 1640,36</t>
+          <t>150,86; 1748,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,28; 933,03</t>
+          <t>60,7; 829,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,83; —</t>
+          <t>60,48; —</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,99</t>
+          <t>2,15; 4,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,62</t>
+          <t>3,78; 5,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,65</t>
+          <t>2,0; 3,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,78</t>
+          <t>1,98; 3,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>81,59; 222,67</t>
+          <t>79,37; 217,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>221,47; 535,8</t>
+          <t>216,49; 535,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>130,28; 361,75</t>
+          <t>127,53; 354,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84,72; 237,71</t>
+          <t>87,24; 239,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>421,78%</t>
+          <t>389,36%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,22</t>
+          <t>1,12; 8,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 7,13</t>
+          <t>0,3; 7,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,91</t>
+          <t>2,88; 9,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,56</t>
+          <t>3,43; 8,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 730,78</t>
+          <t>6,07; 799,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 636,38</t>
+          <t>-13,1; 706,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,2; 2978,21</t>
+          <t>65,66; 2598,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121,23; 1558,25</t>
+          <t>125,58; 1216,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>140,25%</t>
+          <t>141,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,82</t>
+          <t>-0,08; 4,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,54</t>
+          <t>1,39; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,75</t>
+          <t>-0,64; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,88</t>
+          <t>0,02; 3,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 590,46</t>
+          <t>-13,27; 510,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,72; 901,04</t>
+          <t>24,5; 1252,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 553,03</t>
+          <t>-44,35; 455,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 642,08</t>
+          <t>-5,89; 810,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,76</t>
+          <t>1,39; 7,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,4</t>
+          <t>1,57; 6,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,67</t>
+          <t>1,34; 5,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,25</t>
+          <t>0,61; 6,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,12; 1874,91</t>
+          <t>-1,41; 1864,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,87; 1606,58</t>
+          <t>48,92; 979,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,77; —</t>
+          <t>76,74; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 220,18</t>
+          <t>2,13; 234,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>161,15%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,86</t>
+          <t>0,89; 7,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,28</t>
+          <t>3,85; 10,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,64</t>
+          <t>3,12; 9,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,59</t>
+          <t>-0,25; 3,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 349,22</t>
+          <t>14,15; 352,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>121,54; 1706,45</t>
+          <t>113,64; 1566,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>109,5; 1382,85</t>
+          <t>97,56; 1370,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 584,35</t>
+          <t>-50,17; 891,65</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>186,02%</t>
+          <t>181,81%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,89</t>
+          <t>1,99; 9,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,81</t>
+          <t>3,52; 12,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,85</t>
+          <t>0,85; 5,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,0</t>
+          <t>2,31; 8,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,86; 1872,79</t>
+          <t>50,37; 1980,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,0; 588,95</t>
+          <t>46,14; 493,99</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>143,45%</t>
+          <t>139,84%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,49</t>
+          <t>1,6; 8,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,62</t>
+          <t>1,85; 7,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,79</t>
+          <t>0,05; 5,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,68</t>
+          <t>1,32; 6,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,1; 1131,97</t>
+          <t>28,99; 1055,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,61; —</t>
+          <t>56,05; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 1747,41</t>
+          <t>-39,58; 1433,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,35; 353,99</t>
+          <t>30,61; 358,07</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,14</t>
+          <t>1,07; 6,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,45</t>
+          <t>3,25; 7,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,2</t>
+          <t>-0,9; 3,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 5,79</t>
+          <t>2,03; 7,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,28; 301,72</t>
+          <t>22,96; 308,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>106,66; 1015,72</t>
+          <t>121,13; 1043,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 197,89</t>
+          <t>-27,22; 179,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 154,07</t>
+          <t>30,23; 197,91</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>912,19%</t>
+          <t>692,76%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,53</t>
+          <t>-0,71; 2,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,51</t>
+          <t>2,02; 5,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,31</t>
+          <t>1,27; 4,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,69</t>
+          <t>0,91; 2,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 163,07</t>
+          <t>-26,13; 162,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>150,86; 1748,63</t>
+          <t>143,73; 1730,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,7; 829,2</t>
+          <t>71,03; 885,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,48; —</t>
+          <t>88,34; —</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>148,7%</t>
+          <t>145,79%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,06</t>
+          <t>2,09; 4,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,63</t>
+          <t>3,78; 5,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,69</t>
+          <t>2,09; 3,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,88</t>
+          <t>2,42; 3,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79,37; 217,92</t>
+          <t>78,61; 215,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>216,49; 535,91</t>
+          <t>219,64; 572,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>127,53; 354,21</t>
+          <t>129,27; 367,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>87,24; 239,65</t>
+          <t>92,95; 213,25</t>
         </is>
       </c>
     </row>
